--- a/data/trans_bre/IP09-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-30,52; 25,21</t>
+          <t>-31,36; 21,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 42,76</t>
+          <t>-20,64; 38,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-42,93; 33,88</t>
+          <t>-46,31; 27,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,07; 88,01</t>
+          <t>6,74; 90,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,24 +685,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,36; 212,8</t>
+          <t>-40,68; 163,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 230,42</t>
+          <t>-100,0; 186,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,81; —</t>
+          <t>-10,62; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 60,94</t>
+          <t>1,71; 60,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 28,34</t>
+          <t>-35,1; 31,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,02; 80,17</t>
+          <t>-28,92; 80,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-66,69; 12,9</t>
+          <t>-64,59; 12,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,04; 1096,6</t>
+          <t>-13,49; 1140,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,37; 101,52</t>
+          <t>-57,23; 129,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,53; 416,06</t>
+          <t>-33,44; 428,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 83,51</t>
+          <t>-100,0; 65,36</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-61,74; 21,18</t>
+          <t>-62,12; 29,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-53,53; 26,35</t>
+          <t>-47,51; 24,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,34</t>
+          <t>0,0; 86,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-50,55; 18,85</t>
+          <t>-49,09; 18,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 340,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-87,39; 134,3</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,48; 8,48</t>
+          <t>-55,8; 8,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 74,96</t>
+          <t>-8,83; 72,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,88; 36,64</t>
+          <t>-41,79; 34,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 54,85</t>
+          <t>-6,38; 59,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-68,24; 288,3</t>
+          <t>-72,73; 190,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-58,36; 39,53</t>
+          <t>-59,53; 32,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-74,52; 6,45</t>
+          <t>-76,29; 10,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,34 +1075,34 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -20,11</t>
+          <t>-100,0; -16,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 384,11</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 55,11</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 41,99</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -13,34</t>
+          <t>-100,0; -10,06</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,13; 87,5</t>
+          <t>-38,18; 87,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,22; 47,13</t>
+          <t>-33,66; 41,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-48,04; 19,18</t>
+          <t>-46,94; 27,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-51,34; -10,94</t>
+          <t>-55,03; -10,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-54,09; 29,03</t>
+          <t>-49,04; 43,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-61,98; -17,89</t>
+          <t>-62,61; -21,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 48,39</t>
+          <t>-10,65; 47,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-33,35; 32,5</t>
+          <t>-28,88; 30,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-30,23; 29,56</t>
+          <t>-27,25; 31,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,94; 369,18</t>
+          <t>-31,23; 333,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-73,9; 185,44</t>
+          <t>-70,19; 179,55</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,26; 25,53</t>
+          <t>-26,71; 27,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,61; 13,81</t>
+          <t>-27,39; 15,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,01; 3,29</t>
+          <t>-67,06; 4,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-22,84; 55,76</t>
+          <t>-24,32; 57,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-72,63; 131,97</t>
+          <t>-69,26; 158,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-73,51; 92,69</t>
+          <t>-72,6; 96,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-85,49; 7,34</t>
+          <t>-82,9; 16,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-33,51; 247,33</t>
+          <t>-34,84; 276,8</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 5,29</t>
+          <t>-16,19; 7,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 11,57</t>
+          <t>-9,3; 14,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 10,05</t>
+          <t>-20,76; 9,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 29,73</t>
+          <t>-6,82; 30,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-54,18; 22,33</t>
+          <t>-49,43; 33,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-30,34; 39,18</t>
+          <t>-24,83; 51,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-39,86; 26,04</t>
+          <t>-39,54; 27,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 133,41</t>
+          <t>-19,68; 143,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP09-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-31,36; 21,07</t>
+          <t>-31,55; 20,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,64; 38,03</t>
+          <t>-22,23; 36,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-46,31; 27,74</t>
+          <t>-44,1; 31,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,74; 90,02</t>
+          <t>7,42; 87,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,68; 163,48</t>
+          <t>-43,26; 135,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 186,48</t>
+          <t>-100,0; 228,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,62; —</t>
+          <t>-10,77; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 60,82</t>
+          <t>1,21; 61,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,1; 31,88</t>
+          <t>-33,35; 28,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-28,92; 80,41</t>
+          <t>-28,27; 80,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-64,59; 12,88</t>
+          <t>-65,16; 11,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 1140,37</t>
+          <t>-17,92; 1055,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,23; 129,73</t>
+          <t>-56,17; 104,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 428,64</t>
+          <t>-33,02; 413,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 65,36</t>
+          <t>-100,0; 69,47</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-62,12; 29,83</t>
+          <t>-62,09; 30,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-47,51; 24,35</t>
+          <t>-47,24; 24,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 86,46</t>
+          <t>0,0; 80,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-49,09; 18,01</t>
+          <t>-50,07; 23,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,29; 212,91</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-55,8; 8,25</t>
+          <t>-54,11; 8,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 72,34</t>
+          <t>-8,62; 71,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,79; 34,71</t>
+          <t>-39,62; 35,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 59,28</t>
+          <t>-4,84; 63,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,73; 190,78</t>
+          <t>-69,74; 248,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,33; —</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-59,53; 32,75</t>
+          <t>-59,84; 43,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-76,29; 10,1</t>
+          <t>-74,99; 5,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -16,49</t>
+          <t>-100,0; -20,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 384,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 55,11</t>
+          <t>-100,0; 66,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -10,06</t>
+          <t>-100,0; -19,32</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 87,77</t>
+          <t>-38,42; 87,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-33,66; 41,03</t>
+          <t>-32,34; 44,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,94; 27,49</t>
+          <t>-46,28; 26,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-55,03; -10,7</t>
+          <t>-52,69; -11,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-49,04; 43,11</t>
+          <t>-47,64; 34,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-62,61; -21,83</t>
+          <t>-61,92; -21,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 47,12</t>
+          <t>-10,76; 45,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-28,88; 30,41</t>
+          <t>-34,13; 28,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-27,25; 31,2</t>
+          <t>-26,41; 35,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,23; 333,14</t>
+          <t>-26,54; 307,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-70,19; 179,55</t>
+          <t>-64,38; 240,73</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 27,58</t>
+          <t>-24,54; 24,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-27,39; 15,43</t>
+          <t>-27,11; 14,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-67,06; 4,88</t>
+          <t>-69,99; 3,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,32; 57,35</t>
+          <t>-19,89; 59,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-69,26; 158,79</t>
+          <t>-67,36; 122,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-72,6; 96,0</t>
+          <t>-72,12; 82,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-82,9; 16,74</t>
+          <t>-87,64; 5,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,84; 276,8</t>
+          <t>-30,62; 304,96</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 7,57</t>
+          <t>-18,16; 6,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 14,19</t>
+          <t>-9,98; 12,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 9,82</t>
+          <t>-22,23; 10,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 30,64</t>
+          <t>-6,27; 28,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-49,43; 33,17</t>
+          <t>-53,53; 28,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 51,69</t>
+          <t>-26,18; 46,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-39,54; 27,42</t>
+          <t>-41,37; 26,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 143,75</t>
+          <t>-16,84; 127,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP09-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48,25</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>266,89%</t>
+          <t>144,73%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-31,55; 20,5</t>
+          <t>-30,52; 25,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 36,0</t>
+          <t>-20,3; 42,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-44,1; 31,15</t>
+          <t>-42,93; 33,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,42; 87,99</t>
+          <t>-10,01; 61,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,26; 135,59</t>
+          <t>-40,36; 212,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 228,97</t>
+          <t>-100,0; 230,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,77; —</t>
+          <t>-40,07; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-30,92</t>
+          <t>-34,92</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-59,79%</t>
+          <t>-64,59%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 61,31</t>
+          <t>-1,77; 60,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,35; 28,78</t>
+          <t>-37,06; 28,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-28,27; 80,52</t>
+          <t>-31,02; 80,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-65,16; 11,08</t>
+          <t>-69,54; 7,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 1055,01</t>
+          <t>-25,04; 1096,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,17; 104,1</t>
+          <t>-62,37; 101,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,02; 413,26</t>
+          <t>-33,53; 416,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 69,47</t>
+          <t>-100,0; 66,6</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-15,19</t>
+          <t>-11,65</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-39,82%</t>
+          <t>-30,78%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-62,09; 30,32</t>
+          <t>-61,74; 21,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-47,24; 24,73</t>
+          <t>-53,53; 26,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,89</t>
+          <t>0,0; 82,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-50,07; 23,96</t>
+          <t>-48,21; 23,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 340,27</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-87,29; 212,91</t>
+          <t>-84,75; 155,74</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,67</t>
+          <t>22,44</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>284,52%</t>
+          <t>275,07%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-54,11; 8,05</t>
+          <t>-53,48; 8,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 71,9</t>
+          <t>-8,61; 74,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,62; 35,76</t>
+          <t>-37,88; 36,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 63,87</t>
+          <t>-7,26; 54,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-69,74; 248,97</t>
+          <t>-68,24; 288,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-89,33; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-71,38</t>
+          <t>-69,48</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-83,17%</t>
+          <t>-81,16%</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-59,84; 43,16</t>
+          <t>-58,36; 39,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-74,99; 5,46</t>
+          <t>-74,52; 6,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -20,44</t>
+          <t>-100,0; -16,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 66,51</t>
+          <t>-100,0; 41,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -19,32</t>
+          <t>-100,0; -8,31</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-27,87</t>
+          <t>-28,9</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 87,47</t>
+          <t>-38,13; 87,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,34; 44,79</t>
+          <t>-32,22; 47,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,28; 26,82</t>
+          <t>-48,04; 19,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,69; -11,05</t>
+          <t>-53,16; -11,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-47,64; 34,61</t>
+          <t>-54,09; 29,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>-1,41</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>-4,37%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-61,92; -21,65</t>
+          <t>-61,98; -17,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 45,17</t>
+          <t>-12,08; 48,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-34,13; 28,45</t>
+          <t>-33,35; 32,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-26,41; 35,02</t>
+          <t>-33,16; 27,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,54; 307,94</t>
+          <t>-31,94; 369,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-64,38; 240,73</t>
+          <t>-77,12; 148,46</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16,97</t>
+          <t>20,22</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,54; 24,4</t>
+          <t>-25,26; 25,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-27,11; 14,42</t>
+          <t>-28,61; 13,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,99; 3,04</t>
+          <t>-70,01; 3,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 59,41</t>
+          <t>-20,98; 59,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-67,36; 122,09</t>
+          <t>-72,63; 131,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-72,12; 82,86</t>
+          <t>-73,51; 92,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-87,64; 5,95</t>
+          <t>-85,49; 7,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,62; 304,96</t>
+          <t>-29,04; 305,9</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8,18</t>
+          <t>1,65</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 6,31</t>
+          <t>-18,11; 5,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 12,91</t>
+          <t>-12,28; 11,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 10,42</t>
+          <t>-20,83; 10,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 28,67</t>
+          <t>-12,18; 16,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-53,53; 28,79</t>
+          <t>-54,18; 22,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 46,77</t>
+          <t>-30,34; 39,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-41,37; 26,34</t>
+          <t>-39,86; 26,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 127,28</t>
+          <t>-31,07; 71,84</t>
         </is>
       </c>
     </row>
